--- a/Lab3.1/6bai.xlsx
+++ b/Lab3.1/6bai.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ki2Nam4\Testing\Testing_Lab\Lab4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ki2Nam4\Testing\Testing_Lab\Lab3.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{690168F4-A017-4E99-8BFA-30BB2848DD25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0EA3DA-E611-4A36-8068-CBA13E74C2FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3840" yWindow="3840" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bai1" sheetId="1" r:id="rId1"/>
     <sheet name="Bai2" sheetId="2" r:id="rId2"/>
-    <sheet name="Bai3" sheetId="3" r:id="rId3"/>
-    <sheet name="Bai4" sheetId="4" r:id="rId4"/>
+    <sheet name="Bai4" sheetId="4" r:id="rId3"/>
+    <sheet name="Bai3" sheetId="3" r:id="rId4"/>
     <sheet name="Bai5" sheetId="5" r:id="rId5"/>
     <sheet name="Bai6" sheetId="6" r:id="rId6"/>
   </sheets>
@@ -1553,7 +1553,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1611,27 +1611,19 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1640,15 +1632,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -3582,6 +3565,994 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D0B87FC-C04A-404E-A032-CEDD4F826541}">
+  <dimension ref="A1:O76"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="47.6640625" customWidth="1"/>
+    <col min="4" max="4" width="39.5546875" customWidth="1"/>
+    <col min="5" max="5" width="31.109375" customWidth="1"/>
+    <col min="6" max="6" width="27.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="17"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D15" s="14"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D16" s="14"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D17" s="14"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D18" s="14"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="14"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B30" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B34" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="9"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B35" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B36" s="7"/>
+      <c r="C36" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B37" s="7"/>
+      <c r="C37" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B38" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B39" s="7"/>
+      <c r="C39" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B40" s="7"/>
+      <c r="C40" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B41" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B42" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" s="9"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C43" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C44" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C45" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C46" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B49" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" s="9"/>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C50" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G50" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="K50" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="L50" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="M50" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="N50" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="O50" s="12" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C51" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C52" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C53" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C54" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C55" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C56" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C57" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C58" s="25"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="26"/>
+      <c r="K58" s="26"/>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="15"/>
+      <c r="H59" s="15"/>
+      <c r="I59" s="15"/>
+      <c r="J59" s="15"/>
+      <c r="K59" s="15"/>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B61" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C61" s="9"/>
+      <c r="D61" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C62" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="F62" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G62" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="H62" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="I62" s="12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C63" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="C64" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C65" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C66" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C67" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="3"/>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C68" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I68" s="3"/>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C69" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B70" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C71" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C73" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C74" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E74" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C75" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E75" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="C76" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2E0E024-B6CE-49F1-9280-5B6EDEE1E1D3}">
   <dimension ref="A1:K73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3644,7 +4615,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -3655,7 +4626,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -3666,7 +4637,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -3677,7 +4648,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -3688,13 +4659,13 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="24" t="s">
         <v>218</v>
       </c>
     </row>
@@ -3745,7 +4716,7 @@
       <c r="D17" s="14"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -3754,7 +4725,7 @@
       <c r="D18" s="14"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -3836,7 +4807,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C27" s="3" t="s">
@@ -3853,7 +4824,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C28" s="3" t="s">
@@ -3870,7 +4841,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="24" t="s">
+      <c r="B29" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C29" s="3" t="s">
@@ -3887,7 +4858,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C30" s="3" t="s">
@@ -3904,19 +4875,19 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="24" t="s">
         <v>199</v>
       </c>
-      <c r="D31" s="25" t="s">
+      <c r="D31" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="E31" s="25" t="s">
+      <c r="E31" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="F31" s="25" t="s">
+      <c r="F31" s="24" t="s">
         <v>202</v>
       </c>
     </row>
@@ -4158,7 +5129,7 @@
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C51" s="24" t="s">
+      <c r="C51" s="3" t="s">
         <v>170</v>
       </c>
       <c r="D51" s="3"/>
@@ -4173,7 +5144,7 @@
       <c r="K51" s="3"/>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C52" s="24" t="s">
+      <c r="C52" s="3" t="s">
         <v>171</v>
       </c>
       <c r="D52" s="3" t="s">
@@ -4190,7 +5161,7 @@
       <c r="K52" s="3"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C53" s="24" t="s">
+      <c r="C53" s="3" t="s">
         <v>172</v>
       </c>
       <c r="D53" s="3"/>
@@ -4207,7 +5178,7 @@
       <c r="K53" s="3"/>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C54" s="24" t="s">
+      <c r="C54" s="3" t="s">
         <v>173</v>
       </c>
       <c r="D54" s="3"/>
@@ -4222,7 +5193,7 @@
       <c r="K54" s="3"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C55" s="25" t="s">
+      <c r="C55" s="24" t="s">
         <v>174</v>
       </c>
       <c r="D55" s="23"/>
@@ -4256,11 +5227,9 @@
         <v>104</v>
       </c>
       <c r="C58" s="9"/>
-      <c r="D58" s="26" t="s">
+      <c r="D58" t="s">
         <v>176</v>
       </c>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C59" s="12" t="s">
@@ -4343,7 +5312,7 @@
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C63" s="24" t="s">
+      <c r="C63" s="3" t="s">
         <v>170</v>
       </c>
       <c r="D63" s="3"/>
@@ -4355,7 +5324,7 @@
       <c r="H63" s="3"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C64" s="24" t="s">
+      <c r="C64" s="3" t="s">
         <v>172</v>
       </c>
       <c r="D64" s="3"/>
@@ -4367,7 +5336,7 @@
       <c r="H64" s="3"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C65" s="24" t="s">
+      <c r="C65" s="3" t="s">
         <v>173</v>
       </c>
       <c r="D65" s="3" t="s">
@@ -4379,7 +5348,7 @@
       <c r="H65" s="3"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C66" s="24" t="s">
+      <c r="C66" s="3" t="s">
         <v>174</v>
       </c>
       <c r="D66" s="3"/>
@@ -4440,7 +5409,7 @@
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C72" s="24" t="s">
+      <c r="C72" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D72" s="3" t="s">
@@ -4451,7 +5420,7 @@
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C73" s="24" t="s">
+      <c r="C73" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D73" s="3" t="s">
@@ -4459,996 +5428,6 @@
       </c>
       <c r="E73" s="3" t="s">
         <v>98</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D0B87FC-C04A-404E-A032-CEDD4F826541}">
-  <dimension ref="A1:O76"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="23.33203125" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="47.6640625" customWidth="1"/>
-    <col min="4" max="4" width="39.5546875" customWidth="1"/>
-    <col min="5" max="5" width="31.109375" customWidth="1"/>
-    <col min="6" max="6" width="27.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B2" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>264</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B14" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="17"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B15" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D15" s="14"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="D16" s="14"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D17" s="14"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D18" s="14"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="24"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="14"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B26" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="F27" s="24" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>278</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="25" t="s">
-        <v>279</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B30" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C34" s="9"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="7"/>
-      <c r="C36" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B37" s="7"/>
-      <c r="C37" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B38" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="7"/>
-      <c r="C39" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B40" s="7"/>
-      <c r="C40" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B41" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C41" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B42" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" s="9"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C43" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C44" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C45" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C46" s="27" t="s">
-        <v>228</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B49" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="C49" s="9"/>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C50" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="G50" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="H50" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="I50" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="J50" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="K50" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="L50" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="M50" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="N50" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="O50" s="12" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C51" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="O51" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C52" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C53" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="N53" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="O53" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C54" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I54" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="O54" s="24" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C55" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I55" s="24"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="24"/>
-    </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C56" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="O56" s="24"/>
-    </row>
-    <row r="57" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C57" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="24"/>
-      <c r="J57" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="N57" s="3"/>
-      <c r="O57" s="24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C58" s="28"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-    </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C59" s="30"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="30"/>
-      <c r="H59" s="30"/>
-      <c r="I59" s="30"/>
-      <c r="J59" s="30"/>
-      <c r="K59" s="30"/>
-    </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B61" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C61" s="9"/>
-      <c r="D61" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-    </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C62" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="G62" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="H62" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C63" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C64" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C65" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C66" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I66" s="24" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C67" s="24" t="s">
-        <v>258</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="24"/>
-    </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C68" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I68" s="24"/>
-    </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C69" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H69" s="3"/>
-      <c r="I69" s="24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B70" s="9" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C71" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E71" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="72" spans="2:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C72" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C73" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C74" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E74" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C75" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E75" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C76" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E76" s="3">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5519,41 +5498,41 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="3" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="3" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="36"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="36"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
@@ -5602,7 +5581,7 @@
       <c r="D17" s="14"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="3" t="s">
         <v>330</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -5611,7 +5590,7 @@
       <c r="D18" s="14"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="24"/>
+      <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="14"/>
     </row>
@@ -5689,53 +5668,53 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="D27" s="24" t="s">
+      <c r="D27" s="3" t="s">
         <v>10</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="F27" s="24" t="s">
+      <c r="F27" s="3" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="F28" s="24" t="s">
+      <c r="F28" s="3" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C29" s="24" t="s">
         <v>345</v>
       </c>
-      <c r="D29" s="25" t="s">
+      <c r="D29" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="25" t="s">
+      <c r="E29" s="24" t="s">
         <v>346</v>
       </c>
-      <c r="F29" s="25" t="s">
+      <c r="F29" s="24" t="s">
         <v>334</v>
       </c>
     </row>
@@ -5782,61 +5761,61 @@
       <c r="C34" s="9"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="31"/>
-      <c r="C35" s="31"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="27"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="33" t="s">
+      <c r="B36" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="34" t="s">
+      <c r="C36" s="30" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B37" s="34"/>
-      <c r="C37" s="34" t="s">
+      <c r="B37" s="30"/>
+      <c r="C37" s="30" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B38" s="34"/>
-      <c r="C38" s="34" t="s">
+      <c r="B38" s="30"/>
+      <c r="C38" s="30" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="34"/>
-      <c r="C39" s="34" t="s">
+      <c r="B39" s="30"/>
+      <c r="C39" s="30" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B40" s="34"/>
-      <c r="C40" s="34" t="s">
+      <c r="B40" s="30"/>
+      <c r="C40" s="30" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B41" s="33" t="s">
+      <c r="B41" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="C41" s="34" t="s">
+      <c r="C41" s="30" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B42" s="34"/>
-      <c r="C42" s="34" t="s">
+      <c r="B42" s="30"/>
+      <c r="C42" s="30" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B43" s="34"/>
-      <c r="C43" s="34" t="s">
+      <c r="B43" s="30"/>
+      <c r="C43" s="30" t="s">
         <v>297</v>
       </c>
-      <c r="D43" s="32"/>
+      <c r="D43" s="28"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B44" s="9" t="s">
@@ -6008,7 +5987,7 @@
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C54" s="24" t="s">
+      <c r="C54" s="3" t="s">
         <v>301</v>
       </c>
       <c r="D54" s="3"/>
@@ -6018,12 +5997,12 @@
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
-      <c r="I54" s="24"/>
+      <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C55" s="24" t="s">
+      <c r="C55" s="3" t="s">
         <v>302</v>
       </c>
       <c r="D55" s="3" t="s">
@@ -6037,14 +6016,14 @@
       <c r="H55" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I55" s="24"/>
+      <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
         <v>97</v>
       </c>
       <c r="K55" s="3"/>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C56" s="24" t="s">
+      <c r="C56" s="3" t="s">
         <v>303</v>
       </c>
       <c r="D56" s="3"/>
@@ -6054,12 +6033,12 @@
         <v>97</v>
       </c>
       <c r="H56" s="3"/>
-      <c r="I56" s="24"/>
+      <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C57" s="24" t="s">
+      <c r="C57" s="3" t="s">
         <v>304</v>
       </c>
       <c r="D57" s="3"/>
@@ -6067,7 +6046,7 @@
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
-      <c r="I57" s="24" t="s">
+      <c r="I57" s="3" t="s">
         <v>97</v>
       </c>
       <c r="J57" s="3"/>
@@ -6076,35 +6055,32 @@
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C58" s="28"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="26"/>
+      <c r="K58" s="26"/>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C59" s="30"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="30"/>
-      <c r="H59" s="30"/>
-      <c r="I59" s="30"/>
-      <c r="J59" s="30"/>
-      <c r="K59" s="30"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="15"/>
+      <c r="H59" s="15"/>
+      <c r="I59" s="15"/>
+      <c r="J59" s="15"/>
+      <c r="K59" s="15"/>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B61" s="9" t="s">
         <v>104</v>
       </c>
       <c r="C61" s="9"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C62" s="12" t="s">
@@ -6122,7 +6098,7 @@
       <c r="G62" s="12" t="s">
         <v>314</v>
       </c>
-      <c r="H62" s="29"/>
+      <c r="H62" s="26"/>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C63" s="3" t="s">
@@ -6140,7 +6116,7 @@
       <c r="G63" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H63" s="35"/>
+      <c r="H63" s="15"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C64" s="3" t="s">
@@ -6158,7 +6134,7 @@
       <c r="G64" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="H64" s="35"/>
+      <c r="H64" s="15"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C65" s="3" t="s">
@@ -6176,20 +6152,20 @@
       <c r="G65" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H65" s="35"/>
+      <c r="H65" s="15"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C66" s="24" t="s">
+      <c r="C66" s="3" t="s">
         <v>316</v>
       </c>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
-      <c r="H66" s="35"/>
+      <c r="H66" s="15"/>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C67" s="24" t="s">
+      <c r="C67" s="3" t="s">
         <v>301</v>
       </c>
       <c r="D67" s="3"/>
@@ -6198,10 +6174,10 @@
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
-      <c r="H67" s="35"/>
+      <c r="H67" s="15"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C68" s="24" t="s">
+      <c r="C68" s="3" t="s">
         <v>302</v>
       </c>
       <c r="D68" s="3" t="s">
@@ -6210,10 +6186,10 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="35"/>
+      <c r="H68" s="15"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C69" s="24" t="s">
+      <c r="C69" s="3" t="s">
         <v>303</v>
       </c>
       <c r="D69" s="3"/>
@@ -6222,7 +6198,7 @@
         <v>97</v>
       </c>
       <c r="G69" s="3"/>
-      <c r="H69" s="35"/>
+      <c r="H69" s="15"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B70" s="9" t="s">
@@ -6274,7 +6250,7 @@
       </c>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C75" s="24" t="s">
+      <c r="C75" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D75" s="3" t="s">
@@ -6285,7 +6261,7 @@
       </c>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C76" s="24" t="s">
+      <c r="C76" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D76" s="3" t="s">
@@ -6364,47 +6340,47 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="3" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="3" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="24" t="s">
         <v>365</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="24" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
@@ -6461,46 +6437,46 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="3" t="s">
         <v>370</v>
       </c>
       <c r="C18" s="3">
         <v>7</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="3" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="3" t="s">
         <v>371</v>
       </c>
       <c r="C19" s="3">
         <v>5</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="3" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="24" t="s">
         <v>372</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="24">
         <v>0</v>
       </c>
-      <c r="D20" s="25" t="s">
+      <c r="D20" s="24" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="24" t="s">
         <v>330</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="24" t="s">
         <v>379</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="24" t="s">
         <v>380</v>
       </c>
     </row>
@@ -6586,99 +6562,99 @@
       <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="D27" s="24" t="s">
+      <c r="D27" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="24">
+      <c r="E27" s="3">
         <v>8</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="24">
+      <c r="E28" s="3">
         <v>7</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C29" s="24" t="s">
         <v>385</v>
       </c>
-      <c r="D29" s="25" t="s">
+      <c r="D29" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="24">
         <v>5</v>
       </c>
-      <c r="F29" s="25" t="s">
+      <c r="F29" s="24" t="s">
         <v>357</v>
       </c>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="C30" s="24" t="s">
         <v>386</v>
       </c>
-      <c r="D30" s="25" t="s">
+      <c r="D30" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E30" s="25">
+      <c r="E30" s="24">
         <v>4.9000000000000004</v>
       </c>
-      <c r="F30" s="25" t="s">
+      <c r="F30" s="24" t="s">
         <v>358</v>
       </c>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="24" t="s">
         <v>378</v>
       </c>
-      <c r="D31" s="25" t="s">
+      <c r="D31" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="E31" s="25">
+      <c r="E31" s="24">
         <v>0</v>
       </c>
-      <c r="F31" s="25" t="s">
+      <c r="F31" s="24" t="s">
         <v>358</v>
       </c>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B32" s="3" t="s">
@@ -6845,7 +6821,7 @@
       </c>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C52" s="27" t="s">
+      <c r="C52" s="7" t="s">
         <v>228</v>
       </c>
       <c r="D52" s="7" t="s">
@@ -6862,281 +6838,281 @@
       <c r="C55" s="9"/>
     </row>
     <row r="56" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C56" s="38" t="s">
+      <c r="C56" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="D56" s="38" t="s">
+      <c r="D56" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="E56" s="38" t="s">
+      <c r="E56" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="F56" s="38" t="s">
+      <c r="F56" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="G56" s="38" t="s">
+      <c r="G56" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="H56" s="38" t="s">
+      <c r="H56" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="I56" s="38" t="s">
+      <c r="I56" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="J56" s="29"/>
-      <c r="K56" s="29"/>
-      <c r="L56" s="29"/>
-      <c r="M56" s="29"/>
-      <c r="N56" s="29"/>
-      <c r="O56" s="29"/>
+      <c r="J56" s="26"/>
+      <c r="K56" s="26"/>
+      <c r="L56" s="26"/>
+      <c r="M56" s="26"/>
+      <c r="N56" s="26"/>
+      <c r="O56" s="26"/>
     </row>
     <row r="57" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C57" s="34" t="s">
+      <c r="C57" s="30" t="s">
         <v>391</v>
       </c>
-      <c r="D57" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="E57" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="F57" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="G57" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="H57" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="I57" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="J57" s="35"/>
-      <c r="K57" s="35"/>
-      <c r="L57" s="35"/>
-      <c r="M57" s="35"/>
-      <c r="N57" s="35"/>
-      <c r="O57" s="35"/>
+      <c r="D57" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="E57" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="F57" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="G57" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="H57" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="I57" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+      <c r="L57" s="15"/>
+      <c r="M57" s="15"/>
+      <c r="N57" s="15"/>
+      <c r="O57" s="15"/>
     </row>
     <row r="58" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C58" s="34" t="s">
+      <c r="C58" s="30" t="s">
         <v>392</v>
       </c>
-      <c r="D58" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="E58" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="F58" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="G58" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="H58" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="I58" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="J58" s="35"/>
-      <c r="K58" s="35"/>
-      <c r="L58" s="35"/>
-      <c r="M58" s="35"/>
-      <c r="N58" s="35"/>
-      <c r="O58" s="35"/>
+      <c r="D58" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="E58" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="F58" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="G58" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="H58" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="I58" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="J58" s="15"/>
+      <c r="K58" s="15"/>
+      <c r="L58" s="15"/>
+      <c r="M58" s="15"/>
+      <c r="N58" s="15"/>
+      <c r="O58" s="15"/>
     </row>
     <row r="59" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C59" s="34" t="s">
+      <c r="C59" s="30" t="s">
         <v>393</v>
       </c>
-      <c r="D59" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="E59" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="F59" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="G59" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="H59" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="I59" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="J59" s="35"/>
-      <c r="K59" s="35"/>
-      <c r="L59" s="35"/>
-      <c r="M59" s="35"/>
-      <c r="N59" s="35"/>
-      <c r="O59" s="35"/>
+      <c r="D59" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="F59" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="G59" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="H59" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="I59" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="J59" s="15"/>
+      <c r="K59" s="15"/>
+      <c r="L59" s="15"/>
+      <c r="M59" s="15"/>
+      <c r="N59" s="15"/>
+      <c r="O59" s="15"/>
     </row>
     <row r="60" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C60" s="34" t="s">
+      <c r="C60" s="30" t="s">
         <v>394</v>
       </c>
-      <c r="D60" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="E60" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="F60" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="G60" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="H60" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="I60" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="J60" s="35"/>
-      <c r="K60" s="35"/>
-      <c r="L60" s="35"/>
-      <c r="M60" s="35"/>
-      <c r="N60" s="35"/>
-      <c r="O60" s="37"/>
+      <c r="D60" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="E60" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="F60" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="G60" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="H60" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="I60" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="J60" s="15"/>
+      <c r="K60" s="15"/>
+      <c r="L60" s="15"/>
+      <c r="M60" s="15"/>
+      <c r="N60" s="15"/>
+      <c r="O60" s="15"/>
     </row>
     <row r="61" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C61" s="34" t="s">
+      <c r="C61" s="30" t="s">
         <v>395</v>
       </c>
-      <c r="D61" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="E61" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="F61" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="G61" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="H61" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="I61" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="J61" s="35"/>
-      <c r="K61" s="35"/>
-      <c r="L61" s="35"/>
-      <c r="M61" s="35"/>
-      <c r="N61" s="35"/>
-      <c r="O61" s="37"/>
+      <c r="D61" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="E61" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="F61" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="G61" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="H61" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="I61" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+      <c r="L61" s="15"/>
+      <c r="M61" s="15"/>
+      <c r="N61" s="15"/>
+      <c r="O61" s="15"/>
     </row>
     <row r="62" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C62" s="33" t="s">
+      <c r="C62" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="D62" s="34"/>
-      <c r="E62" s="34"/>
-      <c r="F62" s="34"/>
-      <c r="G62" s="34"/>
-      <c r="H62" s="34"/>
-      <c r="I62" s="34"/>
-      <c r="J62" s="35"/>
-      <c r="K62" s="35"/>
-      <c r="L62" s="35"/>
-      <c r="M62" s="35"/>
-      <c r="N62" s="35"/>
-      <c r="O62" s="37"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="30"/>
+      <c r="H62" s="30"/>
+      <c r="I62" s="30"/>
+      <c r="J62" s="15"/>
+      <c r="K62" s="15"/>
+      <c r="L62" s="15"/>
+      <c r="M62" s="15"/>
+      <c r="N62" s="15"/>
+      <c r="O62" s="15"/>
     </row>
     <row r="63" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C63" s="34" t="s">
+      <c r="C63" s="30" t="s">
         <v>396</v>
       </c>
-      <c r="D63" s="33" t="s">
+      <c r="D63" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="E63" s="34"/>
-      <c r="F63" s="34"/>
-      <c r="G63" s="34"/>
-      <c r="H63" s="34"/>
-      <c r="I63" s="34"/>
-      <c r="J63" s="35"/>
-      <c r="K63" s="35"/>
-      <c r="L63" s="35"/>
-      <c r="M63" s="35"/>
-      <c r="N63" s="35"/>
-      <c r="O63" s="37"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="30"/>
+      <c r="I63" s="30"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
+      <c r="L63" s="15"/>
+      <c r="M63" s="15"/>
+      <c r="N63" s="15"/>
+      <c r="O63" s="15"/>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="C64" s="34" t="s">
+      <c r="C64" s="30" t="s">
         <v>397</v>
       </c>
-      <c r="D64" s="34"/>
-      <c r="E64" s="33" t="s">
+      <c r="D64" s="30"/>
+      <c r="E64" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="F64" s="34"/>
-      <c r="G64" s="34"/>
-      <c r="H64" s="34"/>
-      <c r="I64" s="34"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="26"/>
+      <c r="K64" s="26"/>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C65" s="34" t="s">
+      <c r="C65" s="30" t="s">
         <v>398</v>
       </c>
-      <c r="D65" s="34"/>
-      <c r="E65" s="34"/>
-      <c r="F65" s="33" t="s">
+      <c r="D65" s="30"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="G65" s="34"/>
-      <c r="H65" s="34"/>
-      <c r="I65" s="34"/>
-      <c r="J65" s="30"/>
-      <c r="K65" s="30"/>
+      <c r="G65" s="30"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C66" s="34" t="s">
+      <c r="C66" s="30" t="s">
         <v>399</v>
       </c>
-      <c r="D66" s="34"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="34"/>
-      <c r="G66" s="33" t="s">
+      <c r="D66" s="30"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="H66" s="34"/>
-      <c r="I66" s="34"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="30"/>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C67" s="34" t="s">
+      <c r="C67" s="30" t="s">
         <v>400</v>
       </c>
-      <c r="D67" s="34"/>
-      <c r="E67" s="34"/>
-      <c r="F67" s="34"/>
-      <c r="G67" s="34"/>
-      <c r="H67" s="33" t="s">
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="29" t="s">
         <v>97</v>
       </c>
-      <c r="I67" s="34"/>
+      <c r="I67" s="30"/>
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C68" s="34" t="s">
+      <c r="C68" s="30" t="s">
         <v>401</v>
       </c>
-      <c r="D68" s="34"/>
-      <c r="E68" s="34"/>
-      <c r="F68" s="34"/>
-      <c r="G68" s="34"/>
-      <c r="H68" s="34"/>
-      <c r="I68" s="33" t="s">
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="29" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7154,132 +7130,130 @@
         <v>104</v>
       </c>
       <c r="C71" s="9"/>
-      <c r="D71" s="26" t="s">
+      <c r="D71" t="s">
         <v>176</v>
       </c>
-      <c r="E71" s="26"/>
-      <c r="F71" s="26"/>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C72" s="33" t="s">
+      <c r="C72" s="29" t="s">
         <v>254</v>
       </c>
-      <c r="D72" s="33" t="s">
+      <c r="D72" s="29" t="s">
         <v>410</v>
       </c>
-      <c r="E72" s="33" t="s">
+      <c r="E72" s="29" t="s">
         <v>411</v>
       </c>
-      <c r="F72" s="29"/>
-      <c r="G72" s="29"/>
-      <c r="H72" s="29"/>
-      <c r="I72" s="29"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="26"/>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C73" s="33" t="s">
+      <c r="C73" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="D73" s="34" t="s">
+      <c r="D73" s="30" t="s">
         <v>412</v>
       </c>
-      <c r="E73" s="33" t="s">
+      <c r="E73" s="29" t="s">
         <v>413</v>
       </c>
-      <c r="F73" s="35"/>
-      <c r="G73" s="35"/>
-      <c r="H73" s="35"/>
-      <c r="I73" s="35"/>
+      <c r="F73" s="15"/>
+      <c r="G73" s="15"/>
+      <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C74" s="33" t="s">
+      <c r="C74" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="D74" s="34" t="s">
+      <c r="D74" s="30" t="s">
         <v>414</v>
       </c>
-      <c r="E74" s="33" t="s">
+      <c r="E74" s="29" t="s">
         <v>415</v>
       </c>
-      <c r="F74" s="35"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="35"/>
-      <c r="I74" s="35"/>
+      <c r="F74" s="15"/>
+      <c r="G74" s="15"/>
+      <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C75" s="33" t="s">
+      <c r="C75" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="D75" s="34" t="s">
+      <c r="D75" s="30" t="s">
         <v>416</v>
       </c>
-      <c r="E75" s="33" t="s">
+      <c r="E75" s="29" t="s">
         <v>417</v>
       </c>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
+      <c r="F75" s="15"/>
+      <c r="G75" s="15"/>
+      <c r="H75" s="15"/>
+      <c r="I75" s="15"/>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C76" s="33" t="s">
+      <c r="C76" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="D76" s="34" t="s">
+      <c r="D76" s="30" t="s">
         <v>418</v>
       </c>
-      <c r="E76" s="33" t="s">
+      <c r="E76" s="29" t="s">
         <v>419</v>
       </c>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="37"/>
+      <c r="F76" s="15"/>
+      <c r="G76" s="15"/>
+      <c r="H76" s="15"/>
+      <c r="I76" s="15"/>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C77" s="33" t="s">
+      <c r="C77" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="D77" s="34" t="s">
+      <c r="D77" s="30" t="s">
         <v>420</v>
       </c>
-      <c r="E77" s="33" t="s">
+      <c r="E77" s="29" t="s">
         <v>421</v>
       </c>
-      <c r="F77" s="35"/>
-      <c r="G77" s="35"/>
-      <c r="H77" s="35"/>
-      <c r="I77" s="37"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="15"/>
+      <c r="H77" s="15"/>
+      <c r="I77" s="15"/>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C78" s="33" t="s">
+      <c r="C78" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="D78" s="34" t="s">
+      <c r="D78" s="30" t="s">
         <v>422</v>
       </c>
-      <c r="E78" s="33" t="s">
+      <c r="E78" s="29" t="s">
         <v>423</v>
       </c>
-      <c r="F78" s="35"/>
-      <c r="G78" s="35"/>
-      <c r="H78" s="35"/>
-      <c r="I78" s="37"/>
+      <c r="F78" s="15"/>
+      <c r="G78" s="15"/>
+      <c r="H78" s="15"/>
+      <c r="I78" s="15"/>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="C79" s="36"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="35"/>
-      <c r="G79" s="35"/>
-      <c r="H79" s="35"/>
-      <c r="I79" s="37"/>
+      <c r="C79" s="15"/>
+      <c r="D79" s="15"/>
+      <c r="E79" s="15"/>
+      <c r="F79" s="15"/>
+      <c r="G79" s="15"/>
+      <c r="H79" s="15"/>
+      <c r="I79" s="15"/>
     </row>
     <row r="80" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B80" s="9" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="81" spans="3:7" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C81" s="21" t="s">
         <v>42</v>
       </c>
@@ -7296,7 +7270,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="82" spans="3:7" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C82" s="21" t="s">
         <v>44</v>
       </c>
@@ -7313,7 +7287,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="83" spans="3:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C83" s="21" t="s">
         <v>46</v>
       </c>
@@ -7330,7 +7304,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="84" spans="3:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C84" s="21" t="s">
         <v>47</v>
       </c>
@@ -7347,7 +7321,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="85" spans="3:7" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C85" s="21" t="s">
         <v>48</v>
       </c>
@@ -7364,7 +7338,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="86" spans="3:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C86" s="21" t="s">
         <v>50</v>
       </c>
@@ -7381,7 +7355,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="87" spans="3:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C87" s="21" t="s">
         <v>52</v>
       </c>
@@ -7398,7 +7372,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="88" spans="3:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="3:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C88" s="21" t="s">
         <v>54</v>
       </c>
